--- a/NewShopEntry/LamaFastFood/Lama Fast Food Sekuwa/lamafastfoodSekuwa.xlsx
+++ b/NewShopEntry/LamaFastFood/Lama Fast Food Sekuwa/lamafastfoodSekuwa.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\shop-main\NewShopEntry\LamaFastFood\Lama Fast Food Sekuwa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\lamafast foor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23700E50-C676-4794-8A7A-0D1E09EABD4C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76EF08B6-A0DE-4D3F-936B-5E1785BE4C7D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{54B5B15B-BC8D-4992-85A1-0200F89E7B8A}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>DATE</t>
   </si>
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,245 +513,245 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="46.2" x14ac:dyDescent="0.85">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
     </row>
     <row r="2" spans="1:5" ht="46.2" x14ac:dyDescent="0.85">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>2080</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>520</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>820</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>2520</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>570</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>900</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>2190</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>660</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>550</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>520</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4" t="s">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>1015</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>550</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4" t="s">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>970</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>505</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4" t="s">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>1655</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>660</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4" t="s">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>390</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>900</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="3">
         <v>410</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>360</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>840</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="3">
         <v>940</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
@@ -761,16 +761,16 @@
       <c r="E20" s="1"/>
     </row>
     <row r="21" spans="1:5" ht="46.2" x14ac:dyDescent="0.85">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="3"/>
+      <c r="B21" s="4"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="3">
+      <c r="D21" s="4">
         <f>SUM(B4:B20,E4:E19)</f>
         <v>19235</v>
       </c>
-      <c r="E21" s="3"/>
+      <c r="E21" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
